--- a/_deliverables/Semester_Gradebook_2026-1.xlsx
+++ b/_deliverables/Semester_Gradebook_2026-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mcojx/Vibe Coding/MICE/_deliverables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{634A83D7-9FB0-2944-B647-57CD64D61E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD4D7DF-9F52-4046-A036-15079B513E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16780" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1917,30 +1917,30 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1952,10 +1952,10 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2911,384 +2911,384 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
-      <c r="S1" s="29"/>
-      <c r="T1" s="29"/>
-      <c r="U1" s="29"/>
-      <c r="V1" s="29"/>
-      <c r="W1" s="29"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="29"/>
-      <c r="AA1" s="29"/>
-      <c r="AB1" s="29"/>
-      <c r="AC1" s="29"/>
-      <c r="AD1" s="29"/>
-      <c r="AE1" s="29"/>
-      <c r="AF1" s="29"/>
-      <c r="AG1" s="29"/>
-      <c r="AH1" s="29"/>
-      <c r="AI1" s="29"/>
-      <c r="AJ1" s="29"/>
-      <c r="AK1" s="29"/>
-      <c r="AL1" s="29"/>
-      <c r="AM1" s="29"/>
-      <c r="AN1" s="29"/>
-      <c r="AO1" s="29"/>
-      <c r="AP1" s="29"/>
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="31"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="31"/>
+      <c r="Z1" s="31"/>
+      <c r="AA1" s="31"/>
+      <c r="AB1" s="31"/>
+      <c r="AC1" s="31"/>
+      <c r="AD1" s="31"/>
+      <c r="AE1" s="31"/>
+      <c r="AF1" s="31"/>
+      <c r="AG1" s="31"/>
+      <c r="AH1" s="31"/>
+      <c r="AI1" s="31"/>
+      <c r="AJ1" s="31"/>
+      <c r="AK1" s="31"/>
+      <c r="AL1" s="31"/>
+      <c r="AM1" s="31"/>
+      <c r="AN1" s="31"/>
+      <c r="AO1" s="31"/>
+      <c r="AP1" s="31"/>
     </row>
     <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="29"/>
-      <c r="V2" s="29"/>
-      <c r="W2" s="29"/>
-      <c r="X2" s="29"/>
-      <c r="Y2" s="29"/>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="29"/>
-      <c r="AB2" s="29"/>
-      <c r="AC2" s="29"/>
-      <c r="AD2" s="29"/>
-      <c r="AE2" s="29"/>
-      <c r="AF2" s="29"/>
-      <c r="AG2" s="29"/>
-      <c r="AH2" s="29"/>
-      <c r="AI2" s="29"/>
-      <c r="AJ2" s="29"/>
-      <c r="AK2" s="29"/>
-      <c r="AL2" s="29"/>
-      <c r="AM2" s="29"/>
-      <c r="AN2" s="29"/>
-      <c r="AO2" s="29"/>
-      <c r="AP2" s="29"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="31"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="31"/>
+      <c r="Z2" s="31"/>
+      <c r="AA2" s="31"/>
+      <c r="AB2" s="31"/>
+      <c r="AC2" s="31"/>
+      <c r="AD2" s="31"/>
+      <c r="AE2" s="31"/>
+      <c r="AF2" s="31"/>
+      <c r="AG2" s="31"/>
+      <c r="AH2" s="31"/>
+      <c r="AI2" s="31"/>
+      <c r="AJ2" s="31"/>
+      <c r="AK2" s="31"/>
+      <c r="AL2" s="31"/>
+      <c r="AM2" s="31"/>
+      <c r="AN2" s="31"/>
+      <c r="AO2" s="31"/>
+      <c r="AP2" s="31"/>
     </row>
     <row r="3" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A3" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="29"/>
-      <c r="W3" s="29"/>
-      <c r="X3" s="29"/>
-      <c r="Y3" s="29"/>
-      <c r="Z3" s="29"/>
-      <c r="AA3" s="29"/>
-      <c r="AB3" s="29"/>
-      <c r="AC3" s="29"/>
-      <c r="AD3" s="29"/>
-      <c r="AE3" s="29"/>
-      <c r="AF3" s="29"/>
-      <c r="AG3" s="29"/>
-      <c r="AH3" s="29"/>
-      <c r="AI3" s="29"/>
-      <c r="AJ3" s="29"/>
-      <c r="AK3" s="29"/>
-      <c r="AL3" s="29"/>
-      <c r="AM3" s="29"/>
-      <c r="AN3" s="29"/>
-      <c r="AO3" s="29"/>
-      <c r="AP3" s="29"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="31"/>
+      <c r="P3" s="31"/>
+      <c r="Q3" s="31"/>
+      <c r="R3" s="31"/>
+      <c r="S3" s="31"/>
+      <c r="T3" s="31"/>
+      <c r="U3" s="31"/>
+      <c r="V3" s="31"/>
+      <c r="W3" s="31"/>
+      <c r="X3" s="31"/>
+      <c r="Y3" s="31"/>
+      <c r="Z3" s="31"/>
+      <c r="AA3" s="31"/>
+      <c r="AB3" s="31"/>
+      <c r="AC3" s="31"/>
+      <c r="AD3" s="31"/>
+      <c r="AE3" s="31"/>
+      <c r="AF3" s="31"/>
+      <c r="AG3" s="31"/>
+      <c r="AH3" s="31"/>
+      <c r="AI3" s="31"/>
+      <c r="AJ3" s="31"/>
+      <c r="AK3" s="31"/>
+      <c r="AL3" s="31"/>
+      <c r="AM3" s="31"/>
+      <c r="AN3" s="31"/>
+      <c r="AO3" s="31"/>
+      <c r="AP3" s="31"/>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="29"/>
-      <c r="W5" s="29"/>
-      <c r="X5" s="29"/>
-      <c r="Y5" s="29"/>
-      <c r="Z5" s="29"/>
-      <c r="AA5" s="29"/>
-      <c r="AB5" s="29"/>
-      <c r="AC5" s="29"/>
-      <c r="AD5" s="29"/>
-      <c r="AE5" s="29"/>
-      <c r="AF5" s="29"/>
-      <c r="AG5" s="29"/>
-      <c r="AH5" s="29"/>
-      <c r="AI5" s="29"/>
-      <c r="AJ5" s="29"/>
-      <c r="AK5" s="29"/>
-      <c r="AL5" s="29"/>
-      <c r="AM5" s="29"/>
-      <c r="AN5" s="29"/>
-      <c r="AO5" s="29"/>
-      <c r="AP5" s="29"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="31"/>
+      <c r="P5" s="31"/>
+      <c r="Q5" s="31"/>
+      <c r="R5" s="31"/>
+      <c r="S5" s="31"/>
+      <c r="T5" s="31"/>
+      <c r="U5" s="31"/>
+      <c r="V5" s="31"/>
+      <c r="W5" s="31"/>
+      <c r="X5" s="31"/>
+      <c r="Y5" s="31"/>
+      <c r="Z5" s="31"/>
+      <c r="AA5" s="31"/>
+      <c r="AB5" s="31"/>
+      <c r="AC5" s="31"/>
+      <c r="AD5" s="31"/>
+      <c r="AE5" s="31"/>
+      <c r="AF5" s="31"/>
+      <c r="AG5" s="31"/>
+      <c r="AH5" s="31"/>
+      <c r="AI5" s="31"/>
+      <c r="AJ5" s="31"/>
+      <c r="AK5" s="31"/>
+      <c r="AL5" s="31"/>
+      <c r="AM5" s="31"/>
+      <c r="AN5" s="31"/>
+      <c r="AO5" s="31"/>
+      <c r="AP5" s="31"/>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.2">
-      <c r="A6" s="28" t="str">
+      <c r="A6" s="34" t="str">
         <f>"Number of Students:  "&amp;COUNTA(B15:B51)</f>
         <v>Number of Students:  37</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="H6" s="28" t="str">
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="H6" s="34" t="str">
         <f>"Students Passing:  "&amp;COUNTIF(AP15:AP51,"PASS")</f>
         <v>Students Passing:  36</v>
       </c>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.2">
-      <c r="A7" s="28" t="str">
+      <c r="A7" s="34" t="str">
         <f>"Scheduled Class Meetings:  "&amp;15</f>
         <v>Scheduled Class Meetings:  15</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="H7" s="28" t="str">
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="H7" s="34" t="str">
         <f>"Students Not Passing:  "&amp;COUNTIF(AP15:AP51,"NOT PASS")</f>
         <v>Students Not Passing:  1</v>
       </c>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="31"/>
+      <c r="P7" s="31"/>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.2">
-      <c r="A8" s="28" t="str">
+      <c r="A8" s="34" t="str">
         <f>"Average Attendance:  "&amp;TEXT(IFERROR(AVERAGE(AA15:AA51),0),"0.0%")</f>
         <v>Average Attendance:  62.4%</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="H8" s="28" t="str">
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="H8" s="34" t="str">
         <f>"Students At/Over 4-Absence Limit:  "&amp;COUNTIF(W15:W51,"&gt;=4")</f>
         <v>Students At/Over 4-Absence Limit:  1</v>
       </c>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="31"/>
+      <c r="P8" s="31"/>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.2">
-      <c r="A9" s="28" t="str">
+      <c r="A9" s="34" t="str">
         <f>"Average Speaking Score:  "&amp;"n/a for this course"</f>
         <v>Average Speaking Score:  n/a for this course</v>
       </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="H9" s="28" t="str">
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="H9" s="34" t="str">
         <f>"Students In Progress (ungraded):  "&amp;COUNTIF(AP15:AP51,"IN PROGRESS")</f>
         <v>Students In Progress (ungraded):  0</v>
       </c>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="31"/>
+      <c r="P9" s="31"/>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.2">
-      <c r="A10" s="28" t="str">
+      <c r="A10" s="34" t="str">
         <f>"Average Final Grade:  "&amp;TEXT(IFERROR(AVERAGE(AN15:AN51),0),"0.00")</f>
         <v>Average Final Grade:  62.58</v>
       </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="H10" s="28" t="str">
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="H10" s="34" t="str">
         <f>"Passing Grade Threshold:  "&amp;50</f>
         <v>Passing Grade Threshold:  50</v>
       </c>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="29"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
     </row>
     <row r="12" spans="1:43" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="35" t="s">
+      <c r="A12" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="36" t="s">
         <v>365</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="29"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
       <c r="M12" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="30" t="s">
+      <c r="N12" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="O12" s="29"/>
-      <c r="P12" s="29"/>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="29"/>
-      <c r="S12" s="29"/>
-      <c r="T12" s="29"/>
+      <c r="O12" s="31"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="31"/>
+      <c r="R12" s="31"/>
+      <c r="S12" s="31"/>
+      <c r="T12" s="31"/>
       <c r="U12" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="V12" s="31" t="s">
+      <c r="V12" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="W12" s="29"/>
-      <c r="X12" s="29"/>
-      <c r="Y12" s="29"/>
-      <c r="Z12" s="29"/>
-      <c r="AA12" s="29"/>
-      <c r="AB12" s="29"/>
-      <c r="AC12" s="29"/>
-      <c r="AD12" s="30" t="s">
+      <c r="W12" s="31"/>
+      <c r="X12" s="31"/>
+      <c r="Y12" s="31"/>
+      <c r="Z12" s="31"/>
+      <c r="AA12" s="31"/>
+      <c r="AB12" s="31"/>
+      <c r="AC12" s="31"/>
+      <c r="AD12" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="AE12" s="29"/>
-      <c r="AF12" s="30" t="s">
+      <c r="AE12" s="31"/>
+      <c r="AF12" s="35" t="s">
         <v>440</v>
       </c>
-      <c r="AG12" s="29"/>
-      <c r="AH12" s="30" t="s">
+      <c r="AG12" s="31"/>
+      <c r="AH12" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="AI12" s="29"/>
-      <c r="AJ12" s="30" t="s">
+      <c r="AI12" s="31"/>
+      <c r="AJ12" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="AK12" s="29"/>
-      <c r="AL12" s="30" t="s">
+      <c r="AK12" s="31"/>
+      <c r="AL12" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="AM12" s="29"/>
-      <c r="AN12" s="37" t="s">
+      <c r="AM12" s="31"/>
+      <c r="AN12" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="AO12" s="37"/>
-      <c r="AP12" s="37"/>
-      <c r="AQ12" s="37"/>
+      <c r="AO12" s="41"/>
+      <c r="AP12" s="41"/>
+      <c r="AQ12" s="41"/>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.2">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
       <c r="E13" s="24" t="s">
         <v>472</v>
       </c>
@@ -3354,10 +3354,10 @@
       <c r="AQ13" s="23"/>
     </row>
     <row r="14" spans="1:43" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="29"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
+      <c r="A14" s="31"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
       <c r="E14" s="1" t="s">
         <v>18</v>
       </c>
@@ -3382,7 +3382,7 @@
       <c r="L14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M14" s="29"/>
+      <c r="M14" s="31"/>
       <c r="N14" s="1" t="s">
         <v>26</v>
       </c>
@@ -3404,7 +3404,7 @@
       <c r="T14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="U14" s="29"/>
+      <c r="U14" s="31"/>
       <c r="V14" s="2" t="s">
         <v>33</v>
       </c>
@@ -3468,7 +3468,7 @@
       <c r="AP14" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="AQ14" s="42">
+      <c r="AQ14" s="29">
         <v>0.3</v>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
         <f t="shared" ref="AP15:AP51" si="13">IF(AN15=0,"IN PROGRESS",IF(AN15&gt;=50,"PASS","NOT PASS"))</f>
         <v>PASS</v>
       </c>
-      <c r="AQ15" s="41">
+      <c r="AQ15" s="28">
         <f>AN15*0.3</f>
         <v>18.999999999999996</v>
       </c>
@@ -3735,7 +3735,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ16" s="41">
+      <c r="AQ16" s="28">
         <f t="shared" ref="AQ16:AQ51" si="16">AN16*0.3</f>
         <v>19.2</v>
       </c>
@@ -3869,7 +3869,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ17" s="41">
+      <c r="AQ17" s="28">
         <f t="shared" si="16"/>
         <v>18.999999999999996</v>
       </c>
@@ -4003,7 +4003,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ18" s="41">
+      <c r="AQ18" s="28">
         <f t="shared" si="16"/>
         <v>18.399999999999999</v>
       </c>
@@ -4137,7 +4137,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ19" s="41">
+      <c r="AQ19" s="28">
         <f t="shared" si="16"/>
         <v>18</v>
       </c>
@@ -4271,7 +4271,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ20" s="41">
+      <c r="AQ20" s="28">
         <f t="shared" si="16"/>
         <v>19.149999999999999</v>
       </c>
@@ -4405,7 +4405,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ21" s="41">
+      <c r="AQ21" s="28">
         <f t="shared" si="16"/>
         <v>19.399999999999995</v>
       </c>
@@ -4539,7 +4539,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ22" s="41">
+      <c r="AQ22" s="28">
         <f t="shared" si="16"/>
         <v>19.2</v>
       </c>
@@ -4673,7 +4673,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ23" s="41">
+      <c r="AQ23" s="28">
         <f t="shared" si="16"/>
         <v>18.95</v>
       </c>
@@ -4807,7 +4807,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ24" s="41">
+      <c r="AQ24" s="28">
         <f t="shared" si="16"/>
         <v>19.2</v>
       </c>
@@ -4941,7 +4941,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ25" s="41">
+      <c r="AQ25" s="28">
         <f t="shared" si="16"/>
         <v>18.350000000000001</v>
       </c>
@@ -5075,7 +5075,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ26" s="41">
+      <c r="AQ26" s="28">
         <f t="shared" si="16"/>
         <v>18.599999999999998</v>
       </c>
@@ -5209,7 +5209,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ27" s="41">
+      <c r="AQ27" s="28">
         <f t="shared" si="16"/>
         <v>19.999999999999996</v>
       </c>
@@ -5343,7 +5343,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ28" s="41">
+      <c r="AQ28" s="28">
         <f t="shared" si="16"/>
         <v>19.999999999999996</v>
       </c>
@@ -5477,7 +5477,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ29" s="41">
+      <c r="AQ29" s="28">
         <f t="shared" si="16"/>
         <v>19.399999999999995</v>
       </c>
@@ -5611,7 +5611,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ30" s="41">
+      <c r="AQ30" s="28">
         <f t="shared" si="16"/>
         <v>18.100000000000001</v>
       </c>
@@ -5745,7 +5745,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ31" s="41">
+      <c r="AQ31" s="28">
         <f t="shared" si="16"/>
         <v>18.2</v>
       </c>
@@ -5879,7 +5879,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ32" s="41">
+      <c r="AQ32" s="28">
         <f t="shared" si="16"/>
         <v>18.100000000000001</v>
       </c>
@@ -6013,7 +6013,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ33" s="41">
+      <c r="AQ33" s="28">
         <f t="shared" si="16"/>
         <v>19.2</v>
       </c>
@@ -6147,7 +6147,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ34" s="41">
+      <c r="AQ34" s="28">
         <f t="shared" si="16"/>
         <v>18.55</v>
       </c>
@@ -6281,7 +6281,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ35" s="41">
+      <c r="AQ35" s="28">
         <f t="shared" si="16"/>
         <v>18.999999999999996</v>
       </c>
@@ -6415,7 +6415,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ36" s="41">
+      <c r="AQ36" s="28">
         <f t="shared" si="16"/>
         <v>18.350000000000001</v>
       </c>
@@ -6549,7 +6549,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ37" s="41">
+      <c r="AQ37" s="28">
         <f t="shared" si="16"/>
         <v>19.349999999999998</v>
       </c>
@@ -6683,7 +6683,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ38" s="41">
+      <c r="AQ38" s="28">
         <f t="shared" si="16"/>
         <v>19.399999999999995</v>
       </c>
@@ -6817,7 +6817,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ39" s="41">
+      <c r="AQ39" s="28">
         <f t="shared" si="16"/>
         <v>18.599999999999998</v>
       </c>
@@ -6951,7 +6951,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ40" s="41">
+      <c r="AQ40" s="28">
         <f t="shared" si="16"/>
         <v>18.350000000000001</v>
       </c>
@@ -7085,7 +7085,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ41" s="41">
+      <c r="AQ41" s="28">
         <f t="shared" si="16"/>
         <v>18.599999999999998</v>
       </c>
@@ -7219,7 +7219,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ42" s="41">
+      <c r="AQ42" s="28">
         <f t="shared" si="16"/>
         <v>19.399999999999995</v>
       </c>
@@ -7353,7 +7353,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ43" s="41">
+      <c r="AQ43" s="28">
         <f t="shared" si="16"/>
         <v>19.2</v>
       </c>
@@ -7487,7 +7487,7 @@
         <f t="shared" si="13"/>
         <v>NOT PASS</v>
       </c>
-      <c r="AQ44" s="41">
+      <c r="AQ44" s="28">
         <f t="shared" si="16"/>
         <v>12.999999999999998</v>
       </c>
@@ -7621,7 +7621,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ45" s="41">
+      <c r="AQ45" s="28">
         <f t="shared" si="16"/>
         <v>18.999999999999996</v>
       </c>
@@ -7755,7 +7755,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ46" s="41">
+      <c r="AQ46" s="28">
         <f t="shared" si="16"/>
         <v>18.75</v>
       </c>
@@ -7889,7 +7889,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ47" s="41">
+      <c r="AQ47" s="28">
         <f t="shared" si="16"/>
         <v>19.999999999999996</v>
       </c>
@@ -8023,7 +8023,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ48" s="41">
+      <c r="AQ48" s="28">
         <f t="shared" si="16"/>
         <v>19.149999999999999</v>
       </c>
@@ -8157,7 +8157,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ49" s="41">
+      <c r="AQ49" s="28">
         <f t="shared" si="16"/>
         <v>18.55</v>
       </c>
@@ -8291,7 +8291,7 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ50" s="41">
+      <c r="AQ50" s="28">
         <f t="shared" si="16"/>
         <v>19.399999999999995</v>
       </c>
@@ -8425,13 +8425,26 @@
         <f t="shared" si="13"/>
         <v>PASS</v>
       </c>
-      <c r="AQ51" s="41">
+      <c r="AQ51" s="28">
         <f t="shared" si="16"/>
         <v>18.55</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="H6:P6"/>
+    <mergeCell ref="E12:L12"/>
+    <mergeCell ref="V12:AC12"/>
+    <mergeCell ref="AH12:AI12"/>
+    <mergeCell ref="AJ12:AK12"/>
+    <mergeCell ref="H8:P8"/>
+    <mergeCell ref="U12:U51"/>
+    <mergeCell ref="N12:T12"/>
+    <mergeCell ref="H10:P10"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H9:P9"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="AD12:AE12"/>
     <mergeCell ref="AN12:AQ12"/>
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="B12:B14"/>
@@ -8448,19 +8461,6 @@
     <mergeCell ref="AF12:AG12"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="M12:M51"/>
-    <mergeCell ref="H6:P6"/>
-    <mergeCell ref="E12:L12"/>
-    <mergeCell ref="V12:AC12"/>
-    <mergeCell ref="AH12:AI12"/>
-    <mergeCell ref="AJ12:AK12"/>
-    <mergeCell ref="H8:P8"/>
-    <mergeCell ref="U12:U51"/>
-    <mergeCell ref="N12:T12"/>
-    <mergeCell ref="H10:P10"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H9:P9"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="AD12:AE12"/>
   </mergeCells>
   <conditionalFormatting sqref="E15:L51 N15:T51">
     <cfRule type="cellIs" dxfId="59" priority="1" operator="equal">
@@ -8572,475 +8572,475 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
-      <c r="S1" s="29"/>
-      <c r="T1" s="29"/>
-      <c r="U1" s="29"/>
-      <c r="V1" s="29"/>
-      <c r="W1" s="29"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="29"/>
-      <c r="AA1" s="29"/>
-      <c r="AB1" s="29"/>
-      <c r="AC1" s="29"/>
-      <c r="AD1" s="29"/>
-      <c r="AE1" s="29"/>
-      <c r="AF1" s="29"/>
-      <c r="AG1" s="29"/>
-      <c r="AH1" s="29"/>
-      <c r="AI1" s="29"/>
-      <c r="AJ1" s="29"/>
-      <c r="AK1" s="29"/>
-      <c r="AL1" s="29"/>
-      <c r="AM1" s="29"/>
-      <c r="AN1" s="29"/>
-      <c r="AO1" s="29"/>
-      <c r="AP1" s="29"/>
-      <c r="AQ1" s="29"/>
-      <c r="AR1" s="29"/>
-      <c r="AS1" s="29"/>
-      <c r="AT1" s="29"/>
-      <c r="AU1" s="29"/>
-      <c r="AV1" s="29"/>
-      <c r="AW1" s="29"/>
-      <c r="AX1" s="29"/>
-      <c r="AY1" s="29"/>
-      <c r="AZ1" s="29"/>
-      <c r="BA1" s="29"/>
-      <c r="BB1" s="29"/>
-      <c r="BC1" s="29"/>
-      <c r="BD1" s="29"/>
-      <c r="BE1" s="29"/>
-      <c r="BF1" s="29"/>
-      <c r="BG1" s="29"/>
-      <c r="BH1" s="29"/>
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="31"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="31"/>
+      <c r="Z1" s="31"/>
+      <c r="AA1" s="31"/>
+      <c r="AB1" s="31"/>
+      <c r="AC1" s="31"/>
+      <c r="AD1" s="31"/>
+      <c r="AE1" s="31"/>
+      <c r="AF1" s="31"/>
+      <c r="AG1" s="31"/>
+      <c r="AH1" s="31"/>
+      <c r="AI1" s="31"/>
+      <c r="AJ1" s="31"/>
+      <c r="AK1" s="31"/>
+      <c r="AL1" s="31"/>
+      <c r="AM1" s="31"/>
+      <c r="AN1" s="31"/>
+      <c r="AO1" s="31"/>
+      <c r="AP1" s="31"/>
+      <c r="AQ1" s="31"/>
+      <c r="AR1" s="31"/>
+      <c r="AS1" s="31"/>
+      <c r="AT1" s="31"/>
+      <c r="AU1" s="31"/>
+      <c r="AV1" s="31"/>
+      <c r="AW1" s="31"/>
+      <c r="AX1" s="31"/>
+      <c r="AY1" s="31"/>
+      <c r="AZ1" s="31"/>
+      <c r="BA1" s="31"/>
+      <c r="BB1" s="31"/>
+      <c r="BC1" s="31"/>
+      <c r="BD1" s="31"/>
+      <c r="BE1" s="31"/>
+      <c r="BF1" s="31"/>
+      <c r="BG1" s="31"/>
+      <c r="BH1" s="31"/>
     </row>
     <row r="2" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A2" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="29"/>
-      <c r="V2" s="29"/>
-      <c r="W2" s="29"/>
-      <c r="X2" s="29"/>
-      <c r="Y2" s="29"/>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="29"/>
-      <c r="AB2" s="29"/>
-      <c r="AC2" s="29"/>
-      <c r="AD2" s="29"/>
-      <c r="AE2" s="29"/>
-      <c r="AF2" s="29"/>
-      <c r="AG2" s="29"/>
-      <c r="AH2" s="29"/>
-      <c r="AI2" s="29"/>
-      <c r="AJ2" s="29"/>
-      <c r="AK2" s="29"/>
-      <c r="AL2" s="29"/>
-      <c r="AM2" s="29"/>
-      <c r="AN2" s="29"/>
-      <c r="AO2" s="29"/>
-      <c r="AP2" s="29"/>
-      <c r="AQ2" s="29"/>
-      <c r="AR2" s="29"/>
-      <c r="AS2" s="29"/>
-      <c r="AT2" s="29"/>
-      <c r="AU2" s="29"/>
-      <c r="AV2" s="29"/>
-      <c r="AW2" s="29"/>
-      <c r="AX2" s="29"/>
-      <c r="AY2" s="29"/>
-      <c r="AZ2" s="29"/>
-      <c r="BA2" s="29"/>
-      <c r="BB2" s="29"/>
-      <c r="BC2" s="29"/>
-      <c r="BD2" s="29"/>
-      <c r="BE2" s="29"/>
-      <c r="BF2" s="29"/>
-      <c r="BG2" s="29"/>
-      <c r="BH2" s="29"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="31"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="31"/>
+      <c r="Z2" s="31"/>
+      <c r="AA2" s="31"/>
+      <c r="AB2" s="31"/>
+      <c r="AC2" s="31"/>
+      <c r="AD2" s="31"/>
+      <c r="AE2" s="31"/>
+      <c r="AF2" s="31"/>
+      <c r="AG2" s="31"/>
+      <c r="AH2" s="31"/>
+      <c r="AI2" s="31"/>
+      <c r="AJ2" s="31"/>
+      <c r="AK2" s="31"/>
+      <c r="AL2" s="31"/>
+      <c r="AM2" s="31"/>
+      <c r="AN2" s="31"/>
+      <c r="AO2" s="31"/>
+      <c r="AP2" s="31"/>
+      <c r="AQ2" s="31"/>
+      <c r="AR2" s="31"/>
+      <c r="AS2" s="31"/>
+      <c r="AT2" s="31"/>
+      <c r="AU2" s="31"/>
+      <c r="AV2" s="31"/>
+      <c r="AW2" s="31"/>
+      <c r="AX2" s="31"/>
+      <c r="AY2" s="31"/>
+      <c r="AZ2" s="31"/>
+      <c r="BA2" s="31"/>
+      <c r="BB2" s="31"/>
+      <c r="BC2" s="31"/>
+      <c r="BD2" s="31"/>
+      <c r="BE2" s="31"/>
+      <c r="BF2" s="31"/>
+      <c r="BG2" s="31"/>
+      <c r="BH2" s="31"/>
     </row>
     <row r="3" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A3" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="29"/>
-      <c r="W3" s="29"/>
-      <c r="X3" s="29"/>
-      <c r="Y3" s="29"/>
-      <c r="Z3" s="29"/>
-      <c r="AA3" s="29"/>
-      <c r="AB3" s="29"/>
-      <c r="AC3" s="29"/>
-      <c r="AD3" s="29"/>
-      <c r="AE3" s="29"/>
-      <c r="AF3" s="29"/>
-      <c r="AG3" s="29"/>
-      <c r="AH3" s="29"/>
-      <c r="AI3" s="29"/>
-      <c r="AJ3" s="29"/>
-      <c r="AK3" s="29"/>
-      <c r="AL3" s="29"/>
-      <c r="AM3" s="29"/>
-      <c r="AN3" s="29"/>
-      <c r="AO3" s="29"/>
-      <c r="AP3" s="29"/>
-      <c r="AQ3" s="29"/>
-      <c r="AR3" s="29"/>
-      <c r="AS3" s="29"/>
-      <c r="AT3" s="29"/>
-      <c r="AU3" s="29"/>
-      <c r="AV3" s="29"/>
-      <c r="AW3" s="29"/>
-      <c r="AX3" s="29"/>
-      <c r="AY3" s="29"/>
-      <c r="AZ3" s="29"/>
-      <c r="BA3" s="29"/>
-      <c r="BB3" s="29"/>
-      <c r="BC3" s="29"/>
-      <c r="BD3" s="29"/>
-      <c r="BE3" s="29"/>
-      <c r="BF3" s="29"/>
-      <c r="BG3" s="29"/>
-      <c r="BH3" s="29"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="31"/>
+      <c r="P3" s="31"/>
+      <c r="Q3" s="31"/>
+      <c r="R3" s="31"/>
+      <c r="S3" s="31"/>
+      <c r="T3" s="31"/>
+      <c r="U3" s="31"/>
+      <c r="V3" s="31"/>
+      <c r="W3" s="31"/>
+      <c r="X3" s="31"/>
+      <c r="Y3" s="31"/>
+      <c r="Z3" s="31"/>
+      <c r="AA3" s="31"/>
+      <c r="AB3" s="31"/>
+      <c r="AC3" s="31"/>
+      <c r="AD3" s="31"/>
+      <c r="AE3" s="31"/>
+      <c r="AF3" s="31"/>
+      <c r="AG3" s="31"/>
+      <c r="AH3" s="31"/>
+      <c r="AI3" s="31"/>
+      <c r="AJ3" s="31"/>
+      <c r="AK3" s="31"/>
+      <c r="AL3" s="31"/>
+      <c r="AM3" s="31"/>
+      <c r="AN3" s="31"/>
+      <c r="AO3" s="31"/>
+      <c r="AP3" s="31"/>
+      <c r="AQ3" s="31"/>
+      <c r="AR3" s="31"/>
+      <c r="AS3" s="31"/>
+      <c r="AT3" s="31"/>
+      <c r="AU3" s="31"/>
+      <c r="AV3" s="31"/>
+      <c r="AW3" s="31"/>
+      <c r="AX3" s="31"/>
+      <c r="AY3" s="31"/>
+      <c r="AZ3" s="31"/>
+      <c r="BA3" s="31"/>
+      <c r="BB3" s="31"/>
+      <c r="BC3" s="31"/>
+      <c r="BD3" s="31"/>
+      <c r="BE3" s="31"/>
+      <c r="BF3" s="31"/>
+      <c r="BG3" s="31"/>
+      <c r="BH3" s="31"/>
     </row>
     <row r="5" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A5" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="29"/>
-      <c r="W5" s="29"/>
-      <c r="X5" s="29"/>
-      <c r="Y5" s="29"/>
-      <c r="Z5" s="29"/>
-      <c r="AA5" s="29"/>
-      <c r="AB5" s="29"/>
-      <c r="AC5" s="29"/>
-      <c r="AD5" s="29"/>
-      <c r="AE5" s="29"/>
-      <c r="AF5" s="29"/>
-      <c r="AG5" s="29"/>
-      <c r="AH5" s="29"/>
-      <c r="AI5" s="29"/>
-      <c r="AJ5" s="29"/>
-      <c r="AK5" s="29"/>
-      <c r="AL5" s="29"/>
-      <c r="AM5" s="29"/>
-      <c r="AN5" s="29"/>
-      <c r="AO5" s="29"/>
-      <c r="AP5" s="29"/>
-      <c r="AQ5" s="29"/>
-      <c r="AR5" s="29"/>
-      <c r="AS5" s="29"/>
-      <c r="AT5" s="29"/>
-      <c r="AU5" s="29"/>
-      <c r="AV5" s="29"/>
-      <c r="AW5" s="29"/>
-      <c r="AX5" s="29"/>
-      <c r="AY5" s="29"/>
-      <c r="AZ5" s="29"/>
-      <c r="BA5" s="29"/>
-      <c r="BB5" s="29"/>
-      <c r="BC5" s="29"/>
-      <c r="BD5" s="29"/>
-      <c r="BE5" s="29"/>
-      <c r="BF5" s="29"/>
-      <c r="BG5" s="29"/>
-      <c r="BH5" s="29"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="31"/>
+      <c r="P5" s="31"/>
+      <c r="Q5" s="31"/>
+      <c r="R5" s="31"/>
+      <c r="S5" s="31"/>
+      <c r="T5" s="31"/>
+      <c r="U5" s="31"/>
+      <c r="V5" s="31"/>
+      <c r="W5" s="31"/>
+      <c r="X5" s="31"/>
+      <c r="Y5" s="31"/>
+      <c r="Z5" s="31"/>
+      <c r="AA5" s="31"/>
+      <c r="AB5" s="31"/>
+      <c r="AC5" s="31"/>
+      <c r="AD5" s="31"/>
+      <c r="AE5" s="31"/>
+      <c r="AF5" s="31"/>
+      <c r="AG5" s="31"/>
+      <c r="AH5" s="31"/>
+      <c r="AI5" s="31"/>
+      <c r="AJ5" s="31"/>
+      <c r="AK5" s="31"/>
+      <c r="AL5" s="31"/>
+      <c r="AM5" s="31"/>
+      <c r="AN5" s="31"/>
+      <c r="AO5" s="31"/>
+      <c r="AP5" s="31"/>
+      <c r="AQ5" s="31"/>
+      <c r="AR5" s="31"/>
+      <c r="AS5" s="31"/>
+      <c r="AT5" s="31"/>
+      <c r="AU5" s="31"/>
+      <c r="AV5" s="31"/>
+      <c r="AW5" s="31"/>
+      <c r="AX5" s="31"/>
+      <c r="AY5" s="31"/>
+      <c r="AZ5" s="31"/>
+      <c r="BA5" s="31"/>
+      <c r="BB5" s="31"/>
+      <c r="BC5" s="31"/>
+      <c r="BD5" s="31"/>
+      <c r="BE5" s="31"/>
+      <c r="BF5" s="31"/>
+      <c r="BG5" s="31"/>
+      <c r="BH5" s="31"/>
     </row>
     <row r="6" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A6" s="28" t="str">
+      <c r="A6" s="34" t="str">
         <f>"Number of Students:  "&amp;COUNTA(B15:B52)</f>
         <v>Number of Students:  38</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="H6" s="28" t="str">
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="H6" s="34" t="str">
         <f>"Students Passing:  "&amp;COUNTIF(BH15:BH52,"PASS")</f>
         <v>Students Passing:  38</v>
       </c>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
     </row>
     <row r="7" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A7" s="28" t="str">
+      <c r="A7" s="34" t="str">
         <f>"Scheduled Class Meetings:  "&amp;15</f>
         <v>Scheduled Class Meetings:  15</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="H7" s="28" t="str">
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="H7" s="34" t="str">
         <f>"Students Not Passing:  "&amp;COUNTIF(BH15:BH52,"NOT PASS")</f>
         <v>Students Not Passing:  0</v>
       </c>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="31"/>
+      <c r="P7" s="31"/>
     </row>
     <row r="8" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A8" s="28" t="str">
+      <c r="A8" s="34" t="str">
         <f>"Average Attendance:  "&amp;TEXT(IFERROR(AVERAGE(AA15:AA52),0),"0.0%")</f>
         <v>Average Attendance:  67.8%</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="H8" s="28" t="str">
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="H8" s="34" t="str">
         <f>"Students At/Over 4-Absence Limit:  "&amp;COUNTIF(W15:W52,"&gt;=4")</f>
         <v>Students At/Over 4-Absence Limit:  0</v>
       </c>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="31"/>
+      <c r="P8" s="31"/>
     </row>
     <row r="9" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A9" s="28" t="str">
+      <c r="A9" s="34" t="str">
         <f>"Average Speaking Score:  "&amp;TEXT(IFERROR(AVERAGE(AP15:AP52),0),"0.0")</f>
         <v>Average Speaking Score:  84.9</v>
       </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="H9" s="28" t="str">
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="H9" s="34" t="str">
         <f>"Students In Progress (ungraded):  "&amp;COUNTIF(BH15:BH52,"IN PROGRESS")</f>
         <v>Students In Progress (ungraded):  0</v>
       </c>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="31"/>
+      <c r="P9" s="31"/>
     </row>
     <row r="10" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A10" s="28" t="str">
+      <c r="A10" s="34" t="str">
         <f>"Average Final Grade:  "&amp;TEXT(IFERROR(AVERAGE(BF15:BF52),0),"0.00")</f>
         <v>Average Final Grade:  66.80</v>
       </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="H10" s="28" t="str">
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="H10" s="34" t="str">
         <f>"Passing Grade Threshold:  "&amp;50</f>
         <v>Passing Grade Threshold:  50</v>
       </c>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="29"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
     </row>
     <row r="12" spans="1:60" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="35" t="s">
+      <c r="A12" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="36" t="s">
         <v>365</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="29"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
       <c r="M12" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="30" t="s">
+      <c r="N12" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="O12" s="29"/>
-      <c r="P12" s="29"/>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="29"/>
-      <c r="S12" s="29"/>
-      <c r="T12" s="29"/>
+      <c r="O12" s="31"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="31"/>
+      <c r="R12" s="31"/>
+      <c r="S12" s="31"/>
+      <c r="T12" s="31"/>
       <c r="U12" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="V12" s="31" t="s">
+      <c r="V12" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="W12" s="29"/>
-      <c r="X12" s="29"/>
-      <c r="Y12" s="29"/>
-      <c r="Z12" s="29"/>
-      <c r="AA12" s="29"/>
-      <c r="AB12" s="29"/>
-      <c r="AC12" s="29"/>
-      <c r="AD12" s="30" t="s">
+      <c r="W12" s="31"/>
+      <c r="X12" s="31"/>
+      <c r="Y12" s="31"/>
+      <c r="Z12" s="31"/>
+      <c r="AA12" s="31"/>
+      <c r="AB12" s="31"/>
+      <c r="AC12" s="31"/>
+      <c r="AD12" s="35" t="s">
         <v>485</v>
       </c>
-      <c r="AE12" s="29"/>
-      <c r="AF12" s="29"/>
-      <c r="AG12" s="29"/>
-      <c r="AH12" s="29"/>
-      <c r="AI12" s="29"/>
-      <c r="AJ12" s="29"/>
-      <c r="AK12" s="30" t="s">
+      <c r="AE12" s="31"/>
+      <c r="AF12" s="31"/>
+      <c r="AG12" s="31"/>
+      <c r="AH12" s="31"/>
+      <c r="AI12" s="31"/>
+      <c r="AJ12" s="31"/>
+      <c r="AK12" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="AL12" s="29"/>
-      <c r="AM12" s="29"/>
-      <c r="AN12" s="29"/>
-      <c r="AO12" s="29"/>
-      <c r="AP12" s="29"/>
-      <c r="AQ12" s="29"/>
-      <c r="AR12" s="30" t="s">
+      <c r="AL12" s="31"/>
+      <c r="AM12" s="31"/>
+      <c r="AN12" s="31"/>
+      <c r="AO12" s="31"/>
+      <c r="AP12" s="31"/>
+      <c r="AQ12" s="31"/>
+      <c r="AR12" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="AS12" s="29"/>
-      <c r="AT12" s="29"/>
-      <c r="AU12" s="29"/>
-      <c r="AV12" s="29"/>
-      <c r="AW12" s="29"/>
-      <c r="AX12" s="29"/>
-      <c r="AY12" s="30" t="s">
+      <c r="AS12" s="31"/>
+      <c r="AT12" s="31"/>
+      <c r="AU12" s="31"/>
+      <c r="AV12" s="31"/>
+      <c r="AW12" s="31"/>
+      <c r="AX12" s="31"/>
+      <c r="AY12" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="AZ12" s="29"/>
-      <c r="BA12" s="30" t="s">
+      <c r="AZ12" s="31"/>
+      <c r="BA12" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="BB12" s="30"/>
-      <c r="BC12" s="30"/>
-      <c r="BD12" s="30" t="s">
+      <c r="BB12" s="35"/>
+      <c r="BC12" s="35"/>
+      <c r="BD12" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="BE12" s="29"/>
-      <c r="BF12" s="37" t="s">
+      <c r="BE12" s="31"/>
+      <c r="BF12" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="BG12" s="29"/>
-      <c r="BH12" s="29"/>
+      <c r="BG12" s="31"/>
+      <c r="BH12" s="31"/>
     </row>
     <row r="13" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
       <c r="E13" s="22"/>
       <c r="F13" s="23" t="s">
         <v>480</v>
@@ -9130,10 +9130,10 @@
       <c r="BF13" s="22"/>
     </row>
     <row r="14" spans="1:60" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="29"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
+      <c r="A14" s="31"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
       <c r="E14" s="1" t="s">
         <v>130</v>
       </c>
@@ -9158,7 +9158,7 @@
       <c r="L14" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="M14" s="29"/>
+      <c r="M14" s="31"/>
       <c r="N14" s="1" t="s">
         <v>138</v>
       </c>
@@ -9180,7 +9180,7 @@
       <c r="T14" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="U14" s="29"/>
+      <c r="U14" s="31"/>
       <c r="V14" s="2" t="s">
         <v>33</v>
       </c>
@@ -16000,6 +16000,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="BF12:BH12"/>
+    <mergeCell ref="H6:P6"/>
+    <mergeCell ref="E12:L12"/>
+    <mergeCell ref="V12:AC12"/>
+    <mergeCell ref="AY12:AZ12"/>
+    <mergeCell ref="H7:P7"/>
+    <mergeCell ref="BA12:BC12"/>
+    <mergeCell ref="AD12:AJ12"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="AR12:AX12"/>
+    <mergeCell ref="M12:M52"/>
+    <mergeCell ref="U12:U52"/>
     <mergeCell ref="A1:BH1"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="BD12:BE12"/>
@@ -16016,20 +16030,6 @@
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="C12:C14"/>
-    <mergeCell ref="BF12:BH12"/>
-    <mergeCell ref="H6:P6"/>
-    <mergeCell ref="E12:L12"/>
-    <mergeCell ref="V12:AC12"/>
-    <mergeCell ref="AY12:AZ12"/>
-    <mergeCell ref="H7:P7"/>
-    <mergeCell ref="BA12:BC12"/>
-    <mergeCell ref="AD12:AJ12"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="AR12:AX12"/>
-    <mergeCell ref="M12:M52"/>
-    <mergeCell ref="U12:U52"/>
   </mergeCells>
   <conditionalFormatting sqref="E15:L52 N15:T52 E53">
     <cfRule type="cellIs" dxfId="44" priority="1" operator="equal">
@@ -16141,480 +16141,480 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:61" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
-      <c r="S1" s="29"/>
-      <c r="T1" s="29"/>
-      <c r="U1" s="29"/>
-      <c r="V1" s="29"/>
-      <c r="W1" s="29"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="29"/>
-      <c r="AA1" s="29"/>
-      <c r="AB1" s="29"/>
-      <c r="AC1" s="29"/>
-      <c r="AD1" s="29"/>
-      <c r="AE1" s="29"/>
-      <c r="AF1" s="29"/>
-      <c r="AG1" s="29"/>
-      <c r="AH1" s="29"/>
-      <c r="AI1" s="29"/>
-      <c r="AJ1" s="29"/>
-      <c r="AK1" s="29"/>
-      <c r="AL1" s="29"/>
-      <c r="AM1" s="29"/>
-      <c r="AN1" s="29"/>
-      <c r="AO1" s="29"/>
-      <c r="AP1" s="29"/>
-      <c r="AQ1" s="29"/>
-      <c r="AR1" s="29"/>
-      <c r="AS1" s="29"/>
-      <c r="AT1" s="29"/>
-      <c r="AU1" s="29"/>
-      <c r="AV1" s="29"/>
-      <c r="AW1" s="29"/>
-      <c r="AX1" s="29"/>
-      <c r="AY1" s="29"/>
-      <c r="AZ1" s="29"/>
-      <c r="BA1" s="29"/>
-      <c r="BB1" s="29"/>
-      <c r="BC1" s="29"/>
-      <c r="BD1" s="29"/>
-      <c r="BE1" s="29"/>
-      <c r="BF1" s="29"/>
-      <c r="BG1" s="29"/>
-      <c r="BH1" s="29"/>
-      <c r="BI1" s="29"/>
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="31"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="31"/>
+      <c r="Z1" s="31"/>
+      <c r="AA1" s="31"/>
+      <c r="AB1" s="31"/>
+      <c r="AC1" s="31"/>
+      <c r="AD1" s="31"/>
+      <c r="AE1" s="31"/>
+      <c r="AF1" s="31"/>
+      <c r="AG1" s="31"/>
+      <c r="AH1" s="31"/>
+      <c r="AI1" s="31"/>
+      <c r="AJ1" s="31"/>
+      <c r="AK1" s="31"/>
+      <c r="AL1" s="31"/>
+      <c r="AM1" s="31"/>
+      <c r="AN1" s="31"/>
+      <c r="AO1" s="31"/>
+      <c r="AP1" s="31"/>
+      <c r="AQ1" s="31"/>
+      <c r="AR1" s="31"/>
+      <c r="AS1" s="31"/>
+      <c r="AT1" s="31"/>
+      <c r="AU1" s="31"/>
+      <c r="AV1" s="31"/>
+      <c r="AW1" s="31"/>
+      <c r="AX1" s="31"/>
+      <c r="AY1" s="31"/>
+      <c r="AZ1" s="31"/>
+      <c r="BA1" s="31"/>
+      <c r="BB1" s="31"/>
+      <c r="BC1" s="31"/>
+      <c r="BD1" s="31"/>
+      <c r="BE1" s="31"/>
+      <c r="BF1" s="31"/>
+      <c r="BG1" s="31"/>
+      <c r="BH1" s="31"/>
+      <c r="BI1" s="31"/>
     </row>
     <row r="2" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A2" s="39" t="s">
         <v>232</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="29"/>
-      <c r="V2" s="29"/>
-      <c r="W2" s="29"/>
-      <c r="X2" s="29"/>
-      <c r="Y2" s="29"/>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="29"/>
-      <c r="AB2" s="29"/>
-      <c r="AC2" s="29"/>
-      <c r="AD2" s="29"/>
-      <c r="AE2" s="29"/>
-      <c r="AF2" s="29"/>
-      <c r="AG2" s="29"/>
-      <c r="AH2" s="29"/>
-      <c r="AI2" s="29"/>
-      <c r="AJ2" s="29"/>
-      <c r="AK2" s="29"/>
-      <c r="AL2" s="29"/>
-      <c r="AM2" s="29"/>
-      <c r="AN2" s="29"/>
-      <c r="AO2" s="29"/>
-      <c r="AP2" s="29"/>
-      <c r="AQ2" s="29"/>
-      <c r="AR2" s="29"/>
-      <c r="AS2" s="29"/>
-      <c r="AT2" s="29"/>
-      <c r="AU2" s="29"/>
-      <c r="AV2" s="29"/>
-      <c r="AW2" s="29"/>
-      <c r="AX2" s="29"/>
-      <c r="AY2" s="29"/>
-      <c r="AZ2" s="29"/>
-      <c r="BA2" s="29"/>
-      <c r="BB2" s="29"/>
-      <c r="BC2" s="29"/>
-      <c r="BD2" s="29"/>
-      <c r="BE2" s="29"/>
-      <c r="BF2" s="29"/>
-      <c r="BG2" s="29"/>
-      <c r="BH2" s="29"/>
-      <c r="BI2" s="29"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="31"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="31"/>
+      <c r="Z2" s="31"/>
+      <c r="AA2" s="31"/>
+      <c r="AB2" s="31"/>
+      <c r="AC2" s="31"/>
+      <c r="AD2" s="31"/>
+      <c r="AE2" s="31"/>
+      <c r="AF2" s="31"/>
+      <c r="AG2" s="31"/>
+      <c r="AH2" s="31"/>
+      <c r="AI2" s="31"/>
+      <c r="AJ2" s="31"/>
+      <c r="AK2" s="31"/>
+      <c r="AL2" s="31"/>
+      <c r="AM2" s="31"/>
+      <c r="AN2" s="31"/>
+      <c r="AO2" s="31"/>
+      <c r="AP2" s="31"/>
+      <c r="AQ2" s="31"/>
+      <c r="AR2" s="31"/>
+      <c r="AS2" s="31"/>
+      <c r="AT2" s="31"/>
+      <c r="AU2" s="31"/>
+      <c r="AV2" s="31"/>
+      <c r="AW2" s="31"/>
+      <c r="AX2" s="31"/>
+      <c r="AY2" s="31"/>
+      <c r="AZ2" s="31"/>
+      <c r="BA2" s="31"/>
+      <c r="BB2" s="31"/>
+      <c r="BC2" s="31"/>
+      <c r="BD2" s="31"/>
+      <c r="BE2" s="31"/>
+      <c r="BF2" s="31"/>
+      <c r="BG2" s="31"/>
+      <c r="BH2" s="31"/>
+      <c r="BI2" s="31"/>
     </row>
     <row r="3" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A3" s="38" t="s">
         <v>233</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="29"/>
-      <c r="W3" s="29"/>
-      <c r="X3" s="29"/>
-      <c r="Y3" s="29"/>
-      <c r="Z3" s="29"/>
-      <c r="AA3" s="29"/>
-      <c r="AB3" s="29"/>
-      <c r="AC3" s="29"/>
-      <c r="AD3" s="29"/>
-      <c r="AE3" s="29"/>
-      <c r="AF3" s="29"/>
-      <c r="AG3" s="29"/>
-      <c r="AH3" s="29"/>
-      <c r="AI3" s="29"/>
-      <c r="AJ3" s="29"/>
-      <c r="AK3" s="29"/>
-      <c r="AL3" s="29"/>
-      <c r="AM3" s="29"/>
-      <c r="AN3" s="29"/>
-      <c r="AO3" s="29"/>
-      <c r="AP3" s="29"/>
-      <c r="AQ3" s="29"/>
-      <c r="AR3" s="29"/>
-      <c r="AS3" s="29"/>
-      <c r="AT3" s="29"/>
-      <c r="AU3" s="29"/>
-      <c r="AV3" s="29"/>
-      <c r="AW3" s="29"/>
-      <c r="AX3" s="29"/>
-      <c r="AY3" s="29"/>
-      <c r="AZ3" s="29"/>
-      <c r="BA3" s="29"/>
-      <c r="BB3" s="29"/>
-      <c r="BC3" s="29"/>
-      <c r="BD3" s="29"/>
-      <c r="BE3" s="29"/>
-      <c r="BF3" s="29"/>
-      <c r="BG3" s="29"/>
-      <c r="BH3" s="29"/>
-      <c r="BI3" s="29"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="31"/>
+      <c r="P3" s="31"/>
+      <c r="Q3" s="31"/>
+      <c r="R3" s="31"/>
+      <c r="S3" s="31"/>
+      <c r="T3" s="31"/>
+      <c r="U3" s="31"/>
+      <c r="V3" s="31"/>
+      <c r="W3" s="31"/>
+      <c r="X3" s="31"/>
+      <c r="Y3" s="31"/>
+      <c r="Z3" s="31"/>
+      <c r="AA3" s="31"/>
+      <c r="AB3" s="31"/>
+      <c r="AC3" s="31"/>
+      <c r="AD3" s="31"/>
+      <c r="AE3" s="31"/>
+      <c r="AF3" s="31"/>
+      <c r="AG3" s="31"/>
+      <c r="AH3" s="31"/>
+      <c r="AI3" s="31"/>
+      <c r="AJ3" s="31"/>
+      <c r="AK3" s="31"/>
+      <c r="AL3" s="31"/>
+      <c r="AM3" s="31"/>
+      <c r="AN3" s="31"/>
+      <c r="AO3" s="31"/>
+      <c r="AP3" s="31"/>
+      <c r="AQ3" s="31"/>
+      <c r="AR3" s="31"/>
+      <c r="AS3" s="31"/>
+      <c r="AT3" s="31"/>
+      <c r="AU3" s="31"/>
+      <c r="AV3" s="31"/>
+      <c r="AW3" s="31"/>
+      <c r="AX3" s="31"/>
+      <c r="AY3" s="31"/>
+      <c r="AZ3" s="31"/>
+      <c r="BA3" s="31"/>
+      <c r="BB3" s="31"/>
+      <c r="BC3" s="31"/>
+      <c r="BD3" s="31"/>
+      <c r="BE3" s="31"/>
+      <c r="BF3" s="31"/>
+      <c r="BG3" s="31"/>
+      <c r="BH3" s="31"/>
+      <c r="BI3" s="31"/>
     </row>
     <row r="5" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A5" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="29"/>
-      <c r="W5" s="29"/>
-      <c r="X5" s="29"/>
-      <c r="Y5" s="29"/>
-      <c r="Z5" s="29"/>
-      <c r="AA5" s="29"/>
-      <c r="AB5" s="29"/>
-      <c r="AC5" s="29"/>
-      <c r="AD5" s="29"/>
-      <c r="AE5" s="29"/>
-      <c r="AF5" s="29"/>
-      <c r="AG5" s="29"/>
-      <c r="AH5" s="29"/>
-      <c r="AI5" s="29"/>
-      <c r="AJ5" s="29"/>
-      <c r="AK5" s="29"/>
-      <c r="AL5" s="29"/>
-      <c r="AM5" s="29"/>
-      <c r="AN5" s="29"/>
-      <c r="AO5" s="29"/>
-      <c r="AP5" s="29"/>
-      <c r="AQ5" s="29"/>
-      <c r="AR5" s="29"/>
-      <c r="AS5" s="29"/>
-      <c r="AT5" s="29"/>
-      <c r="AU5" s="29"/>
-      <c r="AV5" s="29"/>
-      <c r="AW5" s="29"/>
-      <c r="AX5" s="29"/>
-      <c r="AY5" s="29"/>
-      <c r="AZ5" s="29"/>
-      <c r="BA5" s="29"/>
-      <c r="BB5" s="29"/>
-      <c r="BC5" s="29"/>
-      <c r="BD5" s="29"/>
-      <c r="BE5" s="29"/>
-      <c r="BF5" s="29"/>
-      <c r="BG5" s="29"/>
-      <c r="BH5" s="29"/>
-      <c r="BI5" s="29"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="31"/>
+      <c r="P5" s="31"/>
+      <c r="Q5" s="31"/>
+      <c r="R5" s="31"/>
+      <c r="S5" s="31"/>
+      <c r="T5" s="31"/>
+      <c r="U5" s="31"/>
+      <c r="V5" s="31"/>
+      <c r="W5" s="31"/>
+      <c r="X5" s="31"/>
+      <c r="Y5" s="31"/>
+      <c r="Z5" s="31"/>
+      <c r="AA5" s="31"/>
+      <c r="AB5" s="31"/>
+      <c r="AC5" s="31"/>
+      <c r="AD5" s="31"/>
+      <c r="AE5" s="31"/>
+      <c r="AF5" s="31"/>
+      <c r="AG5" s="31"/>
+      <c r="AH5" s="31"/>
+      <c r="AI5" s="31"/>
+      <c r="AJ5" s="31"/>
+      <c r="AK5" s="31"/>
+      <c r="AL5" s="31"/>
+      <c r="AM5" s="31"/>
+      <c r="AN5" s="31"/>
+      <c r="AO5" s="31"/>
+      <c r="AP5" s="31"/>
+      <c r="AQ5" s="31"/>
+      <c r="AR5" s="31"/>
+      <c r="AS5" s="31"/>
+      <c r="AT5" s="31"/>
+      <c r="AU5" s="31"/>
+      <c r="AV5" s="31"/>
+      <c r="AW5" s="31"/>
+      <c r="AX5" s="31"/>
+      <c r="AY5" s="31"/>
+      <c r="AZ5" s="31"/>
+      <c r="BA5" s="31"/>
+      <c r="BB5" s="31"/>
+      <c r="BC5" s="31"/>
+      <c r="BD5" s="31"/>
+      <c r="BE5" s="31"/>
+      <c r="BF5" s="31"/>
+      <c r="BG5" s="31"/>
+      <c r="BH5" s="31"/>
+      <c r="BI5" s="31"/>
     </row>
     <row r="6" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A6" s="28" t="str">
+      <c r="A6" s="34" t="str">
         <f>"Number of Students:  "&amp;COUNTA(B15:B50)</f>
         <v>Number of Students:  36</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="H6" s="28" t="str">
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="H6" s="34" t="str">
         <f>"Students Passing:  "&amp;COUNTIF(BI15:BI50,"PASS")</f>
-        <v>Students Passing:  31</v>
-      </c>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
+        <v>Students Passing:  32</v>
+      </c>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
     </row>
     <row r="7" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A7" s="28" t="str">
+      <c r="A7" s="34" t="str">
         <f>"Scheduled Class Meetings:  "&amp;15</f>
         <v>Scheduled Class Meetings:  15</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="H7" s="28" t="str">
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="H7" s="34" t="str">
         <f>"Students Not Passing:  "&amp;COUNTIF(BI15:BI50,"NOT PASS")</f>
-        <v>Students Not Passing:  5</v>
-      </c>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
+        <v>Students Not Passing:  4</v>
+      </c>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="31"/>
+      <c r="P7" s="31"/>
     </row>
     <row r="8" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A8" s="28" t="str">
+      <c r="A8" s="34" t="str">
         <f>"Average Attendance:  "&amp;TEXT(IFERROR(AVERAGE(AA15:AA50),0),"0.0%")</f>
         <v>Average Attendance:  52.1%</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="H8" s="28" t="str">
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="H8" s="34" t="str">
         <f>"Students At/Over 4-Absence Limit:  "&amp;COUNTIF(W15:W50,"&gt;=4")</f>
         <v>Students At/Over 4-Absence Limit:  3</v>
       </c>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="31"/>
+      <c r="P8" s="31"/>
     </row>
     <row r="9" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A9" s="28" t="str">
+      <c r="A9" s="34" t="str">
         <f>"Average Speaking Score:  "&amp;TEXT(IFERROR(AVERAGE(AQ15:AQ50),0),"0.0")</f>
-        <v>Average Speaking Score:  79.6</v>
-      </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="H9" s="28" t="str">
+        <v>Average Speaking Score:  80.6</v>
+      </c>
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="H9" s="34" t="str">
         <f>"Students In Progress (ungraded):  "&amp;COUNTIF(BI15:BI50,"IN PROGRESS")</f>
         <v>Students In Progress (ungraded):  0</v>
       </c>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="31"/>
+      <c r="P9" s="31"/>
     </row>
     <row r="10" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A10" s="28" t="str">
+      <c r="A10" s="34" t="str">
         <f>"Average Final Grade:  "&amp;TEXT(IFERROR(AVERAGE(BG15:BG50),0),"0.00")</f>
-        <v>Average Final Grade:  58.04</v>
-      </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="H10" s="28" t="str">
+        <v>Average Final Grade:  58.27</v>
+      </c>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="H10" s="34" t="str">
         <f>"Passing Grade Threshold:  "&amp;50</f>
         <v>Passing Grade Threshold:  50</v>
       </c>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="29"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
     </row>
     <row r="12" spans="1:61" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="35" t="s">
+      <c r="A12" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="36" t="s">
         <v>365</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="29"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
       <c r="M12" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="30" t="s">
+      <c r="N12" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="O12" s="29"/>
-      <c r="P12" s="29"/>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="29"/>
-      <c r="S12" s="29"/>
-      <c r="T12" s="29"/>
+      <c r="O12" s="31"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="31"/>
+      <c r="R12" s="31"/>
+      <c r="S12" s="31"/>
+      <c r="T12" s="31"/>
       <c r="U12" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="V12" s="31" t="s">
+      <c r="V12" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="W12" s="29"/>
-      <c r="X12" s="29"/>
-      <c r="Y12" s="29"/>
-      <c r="Z12" s="29"/>
-      <c r="AA12" s="29"/>
-      <c r="AB12" s="29"/>
-      <c r="AC12" s="29"/>
-      <c r="AD12" s="30" t="s">
+      <c r="W12" s="31"/>
+      <c r="X12" s="31"/>
+      <c r="Y12" s="31"/>
+      <c r="Z12" s="31"/>
+      <c r="AA12" s="31"/>
+      <c r="AB12" s="31"/>
+      <c r="AC12" s="31"/>
+      <c r="AD12" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="AE12" s="29"/>
-      <c r="AF12" s="29"/>
-      <c r="AG12" s="29"/>
-      <c r="AH12" s="29"/>
-      <c r="AI12" s="29"/>
-      <c r="AJ12" s="29"/>
-      <c r="AK12" s="30" t="s">
+      <c r="AE12" s="31"/>
+      <c r="AF12" s="31"/>
+      <c r="AG12" s="31"/>
+      <c r="AH12" s="31"/>
+      <c r="AI12" s="31"/>
+      <c r="AJ12" s="31"/>
+      <c r="AK12" s="35" t="s">
         <v>234</v>
       </c>
-      <c r="AL12" s="29"/>
-      <c r="AM12" s="29"/>
-      <c r="AN12" s="29"/>
-      <c r="AO12" s="29"/>
-      <c r="AP12" s="29"/>
-      <c r="AQ12" s="29"/>
-      <c r="AR12" s="29"/>
-      <c r="AS12" s="30" t="s">
+      <c r="AL12" s="31"/>
+      <c r="AM12" s="31"/>
+      <c r="AN12" s="31"/>
+      <c r="AO12" s="31"/>
+      <c r="AP12" s="31"/>
+      <c r="AQ12" s="31"/>
+      <c r="AR12" s="31"/>
+      <c r="AS12" s="35" t="s">
         <v>235</v>
       </c>
-      <c r="AT12" s="29"/>
-      <c r="AU12" s="29"/>
-      <c r="AV12" s="29"/>
-      <c r="AW12" s="29"/>
-      <c r="AX12" s="29"/>
-      <c r="AY12" s="29"/>
-      <c r="AZ12" s="30" t="s">
+      <c r="AT12" s="31"/>
+      <c r="AU12" s="31"/>
+      <c r="AV12" s="31"/>
+      <c r="AW12" s="31"/>
+      <c r="AX12" s="31"/>
+      <c r="AY12" s="31"/>
+      <c r="AZ12" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="BA12" s="29"/>
-      <c r="BB12" s="30" t="s">
+      <c r="BA12" s="31"/>
+      <c r="BB12" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="BC12" s="30"/>
-      <c r="BD12" s="30"/>
-      <c r="BE12" s="30" t="s">
+      <c r="BC12" s="35"/>
+      <c r="BD12" s="35"/>
+      <c r="BE12" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="BF12" s="29"/>
-      <c r="BG12" s="37" t="s">
+      <c r="BF12" s="31"/>
+      <c r="BG12" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="BH12" s="29"/>
-      <c r="BI12" s="29"/>
+      <c r="BH12" s="31"/>
+      <c r="BI12" s="31"/>
     </row>
     <row r="13" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
       <c r="E13" s="23" t="s">
         <v>514</v>
       </c>
@@ -16705,10 +16705,10 @@
       <c r="BG13" s="25"/>
     </row>
     <row r="14" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="29"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
+      <c r="A14" s="31"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
       <c r="E14" s="1" t="s">
         <v>237</v>
       </c>
@@ -16733,7 +16733,7 @@
       <c r="L14" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="M14" s="29"/>
+      <c r="M14" s="31"/>
       <c r="N14" s="1" t="s">
         <v>245</v>
       </c>
@@ -16755,7 +16755,7 @@
       <c r="T14" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="U14" s="29"/>
+      <c r="U14" s="31"/>
       <c r="V14" s="2" t="s">
         <v>33</v>
       </c>
@@ -19994,14 +19994,16 @@
       </c>
       <c r="AN32" s="8"/>
       <c r="AO32" s="8"/>
-      <c r="AP32" s="8"/>
+      <c r="AP32" s="8">
+        <v>100</v>
+      </c>
       <c r="AQ32" s="16">
         <f t="shared" si="10"/>
-        <v>33.333333333333336</v>
+        <v>50</v>
       </c>
       <c r="AR32" s="13">
         <f t="shared" si="11"/>
-        <v>8.3333333333333339</v>
+        <v>12.5</v>
       </c>
       <c r="AS32" s="8">
         <v>100</v>
@@ -20046,15 +20048,15 @@
       </c>
       <c r="BG32" s="14">
         <f t="shared" si="16"/>
-        <v>47.35</v>
+        <v>51.516666666666673</v>
       </c>
       <c r="BH32" s="15" t="str">
         <f t="shared" si="17"/>
-        <v>E/F</v>
+        <v>D</v>
       </c>
       <c r="BI32" s="15" t="str">
         <f t="shared" si="18"/>
-        <v>NOT PASS</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="33" spans="1:61" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -20171,14 +20173,16 @@
       </c>
       <c r="AN33" s="8"/>
       <c r="AO33" s="8"/>
-      <c r="AP33" s="8"/>
+      <c r="AP33" s="8">
+        <v>100</v>
+      </c>
       <c r="AQ33" s="16">
         <f t="shared" si="10"/>
-        <v>33.333333333333336</v>
+        <v>50</v>
       </c>
       <c r="AR33" s="13">
         <f t="shared" si="11"/>
-        <v>8.3333333333333339</v>
+        <v>12.5</v>
       </c>
       <c r="AS33" s="8">
         <v>100</v>
@@ -20223,7 +20227,7 @@
       </c>
       <c r="BG33" s="14">
         <f t="shared" si="16"/>
-        <v>42.95</v>
+        <v>47.116666666666674</v>
       </c>
       <c r="BH33" s="15" t="str">
         <f t="shared" si="17"/>
@@ -23239,6 +23243,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="H6:P6"/>
+    <mergeCell ref="BG12:BI12"/>
+    <mergeCell ref="E12:L12"/>
+    <mergeCell ref="V12:AC12"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="N12:T12"/>
+    <mergeCell ref="AS12:AY12"/>
+    <mergeCell ref="AZ12:BA12"/>
+    <mergeCell ref="H10:P10"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H9:P9"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="U12:U50"/>
+    <mergeCell ref="BB12:BD12"/>
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="M12:M50"/>
     <mergeCell ref="H7:P7"/>
@@ -23255,20 +23273,6 @@
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A5:BI5"/>
     <mergeCell ref="H8:P8"/>
-    <mergeCell ref="H6:P6"/>
-    <mergeCell ref="BG12:BI12"/>
-    <mergeCell ref="E12:L12"/>
-    <mergeCell ref="V12:AC12"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="N12:T12"/>
-    <mergeCell ref="AS12:AY12"/>
-    <mergeCell ref="AZ12:BA12"/>
-    <mergeCell ref="H10:P10"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H9:P9"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="U12:U50"/>
-    <mergeCell ref="BB12:BD12"/>
   </mergeCells>
   <conditionalFormatting sqref="E15:L50 N15:T50">
     <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
@@ -23380,475 +23384,475 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
-      <c r="S1" s="29"/>
-      <c r="T1" s="29"/>
-      <c r="U1" s="29"/>
-      <c r="V1" s="29"/>
-      <c r="W1" s="29"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="29"/>
-      <c r="AA1" s="29"/>
-      <c r="AB1" s="29"/>
-      <c r="AC1" s="29"/>
-      <c r="AD1" s="29"/>
-      <c r="AE1" s="29"/>
-      <c r="AF1" s="29"/>
-      <c r="AG1" s="29"/>
-      <c r="AH1" s="29"/>
-      <c r="AI1" s="29"/>
-      <c r="AJ1" s="29"/>
-      <c r="AK1" s="29"/>
-      <c r="AL1" s="29"/>
-      <c r="AM1" s="29"/>
-      <c r="AN1" s="29"/>
-      <c r="AO1" s="29"/>
-      <c r="AP1" s="29"/>
-      <c r="AQ1" s="29"/>
-      <c r="AR1" s="29"/>
-      <c r="AS1" s="29"/>
-      <c r="AT1" s="29"/>
-      <c r="AU1" s="29"/>
-      <c r="AV1" s="29"/>
-      <c r="AW1" s="29"/>
-      <c r="AX1" s="29"/>
-      <c r="AY1" s="29"/>
-      <c r="AZ1" s="29"/>
-      <c r="BA1" s="29"/>
-      <c r="BB1" s="29"/>
-      <c r="BC1" s="29"/>
-      <c r="BD1" s="29"/>
-      <c r="BE1" s="29"/>
-      <c r="BF1" s="29"/>
-      <c r="BG1" s="29"/>
-      <c r="BH1" s="29"/>
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="31"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="31"/>
+      <c r="Z1" s="31"/>
+      <c r="AA1" s="31"/>
+      <c r="AB1" s="31"/>
+      <c r="AC1" s="31"/>
+      <c r="AD1" s="31"/>
+      <c r="AE1" s="31"/>
+      <c r="AF1" s="31"/>
+      <c r="AG1" s="31"/>
+      <c r="AH1" s="31"/>
+      <c r="AI1" s="31"/>
+      <c r="AJ1" s="31"/>
+      <c r="AK1" s="31"/>
+      <c r="AL1" s="31"/>
+      <c r="AM1" s="31"/>
+      <c r="AN1" s="31"/>
+      <c r="AO1" s="31"/>
+      <c r="AP1" s="31"/>
+      <c r="AQ1" s="31"/>
+      <c r="AR1" s="31"/>
+      <c r="AS1" s="31"/>
+      <c r="AT1" s="31"/>
+      <c r="AU1" s="31"/>
+      <c r="AV1" s="31"/>
+      <c r="AW1" s="31"/>
+      <c r="AX1" s="31"/>
+      <c r="AY1" s="31"/>
+      <c r="AZ1" s="31"/>
+      <c r="BA1" s="31"/>
+      <c r="BB1" s="31"/>
+      <c r="BC1" s="31"/>
+      <c r="BD1" s="31"/>
+      <c r="BE1" s="31"/>
+      <c r="BF1" s="31"/>
+      <c r="BG1" s="31"/>
+      <c r="BH1" s="31"/>
     </row>
     <row r="2" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A2" s="39" t="s">
         <v>325</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="29"/>
-      <c r="V2" s="29"/>
-      <c r="W2" s="29"/>
-      <c r="X2" s="29"/>
-      <c r="Y2" s="29"/>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="29"/>
-      <c r="AB2" s="29"/>
-      <c r="AC2" s="29"/>
-      <c r="AD2" s="29"/>
-      <c r="AE2" s="29"/>
-      <c r="AF2" s="29"/>
-      <c r="AG2" s="29"/>
-      <c r="AH2" s="29"/>
-      <c r="AI2" s="29"/>
-      <c r="AJ2" s="29"/>
-      <c r="AK2" s="29"/>
-      <c r="AL2" s="29"/>
-      <c r="AM2" s="29"/>
-      <c r="AN2" s="29"/>
-      <c r="AO2" s="29"/>
-      <c r="AP2" s="29"/>
-      <c r="AQ2" s="29"/>
-      <c r="AR2" s="29"/>
-      <c r="AS2" s="29"/>
-      <c r="AT2" s="29"/>
-      <c r="AU2" s="29"/>
-      <c r="AV2" s="29"/>
-      <c r="AW2" s="29"/>
-      <c r="AX2" s="29"/>
-      <c r="AY2" s="29"/>
-      <c r="AZ2" s="29"/>
-      <c r="BA2" s="29"/>
-      <c r="BB2" s="29"/>
-      <c r="BC2" s="29"/>
-      <c r="BD2" s="29"/>
-      <c r="BE2" s="29"/>
-      <c r="BF2" s="29"/>
-      <c r="BG2" s="29"/>
-      <c r="BH2" s="29"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="31"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="31"/>
+      <c r="Z2" s="31"/>
+      <c r="AA2" s="31"/>
+      <c r="AB2" s="31"/>
+      <c r="AC2" s="31"/>
+      <c r="AD2" s="31"/>
+      <c r="AE2" s="31"/>
+      <c r="AF2" s="31"/>
+      <c r="AG2" s="31"/>
+      <c r="AH2" s="31"/>
+      <c r="AI2" s="31"/>
+      <c r="AJ2" s="31"/>
+      <c r="AK2" s="31"/>
+      <c r="AL2" s="31"/>
+      <c r="AM2" s="31"/>
+      <c r="AN2" s="31"/>
+      <c r="AO2" s="31"/>
+      <c r="AP2" s="31"/>
+      <c r="AQ2" s="31"/>
+      <c r="AR2" s="31"/>
+      <c r="AS2" s="31"/>
+      <c r="AT2" s="31"/>
+      <c r="AU2" s="31"/>
+      <c r="AV2" s="31"/>
+      <c r="AW2" s="31"/>
+      <c r="AX2" s="31"/>
+      <c r="AY2" s="31"/>
+      <c r="AZ2" s="31"/>
+      <c r="BA2" s="31"/>
+      <c r="BB2" s="31"/>
+      <c r="BC2" s="31"/>
+      <c r="BD2" s="31"/>
+      <c r="BE2" s="31"/>
+      <c r="BF2" s="31"/>
+      <c r="BG2" s="31"/>
+      <c r="BH2" s="31"/>
     </row>
     <row r="3" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A3" s="38" t="s">
         <v>326</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="29"/>
-      <c r="W3" s="29"/>
-      <c r="X3" s="29"/>
-      <c r="Y3" s="29"/>
-      <c r="Z3" s="29"/>
-      <c r="AA3" s="29"/>
-      <c r="AB3" s="29"/>
-      <c r="AC3" s="29"/>
-      <c r="AD3" s="29"/>
-      <c r="AE3" s="29"/>
-      <c r="AF3" s="29"/>
-      <c r="AG3" s="29"/>
-      <c r="AH3" s="29"/>
-      <c r="AI3" s="29"/>
-      <c r="AJ3" s="29"/>
-      <c r="AK3" s="29"/>
-      <c r="AL3" s="29"/>
-      <c r="AM3" s="29"/>
-      <c r="AN3" s="29"/>
-      <c r="AO3" s="29"/>
-      <c r="AP3" s="29"/>
-      <c r="AQ3" s="29"/>
-      <c r="AR3" s="29"/>
-      <c r="AS3" s="29"/>
-      <c r="AT3" s="29"/>
-      <c r="AU3" s="29"/>
-      <c r="AV3" s="29"/>
-      <c r="AW3" s="29"/>
-      <c r="AX3" s="29"/>
-      <c r="AY3" s="29"/>
-      <c r="AZ3" s="29"/>
-      <c r="BA3" s="29"/>
-      <c r="BB3" s="29"/>
-      <c r="BC3" s="29"/>
-      <c r="BD3" s="29"/>
-      <c r="BE3" s="29"/>
-      <c r="BF3" s="29"/>
-      <c r="BG3" s="29"/>
-      <c r="BH3" s="29"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="31"/>
+      <c r="P3" s="31"/>
+      <c r="Q3" s="31"/>
+      <c r="R3" s="31"/>
+      <c r="S3" s="31"/>
+      <c r="T3" s="31"/>
+      <c r="U3" s="31"/>
+      <c r="V3" s="31"/>
+      <c r="W3" s="31"/>
+      <c r="X3" s="31"/>
+      <c r="Y3" s="31"/>
+      <c r="Z3" s="31"/>
+      <c r="AA3" s="31"/>
+      <c r="AB3" s="31"/>
+      <c r="AC3" s="31"/>
+      <c r="AD3" s="31"/>
+      <c r="AE3" s="31"/>
+      <c r="AF3" s="31"/>
+      <c r="AG3" s="31"/>
+      <c r="AH3" s="31"/>
+      <c r="AI3" s="31"/>
+      <c r="AJ3" s="31"/>
+      <c r="AK3" s="31"/>
+      <c r="AL3" s="31"/>
+      <c r="AM3" s="31"/>
+      <c r="AN3" s="31"/>
+      <c r="AO3" s="31"/>
+      <c r="AP3" s="31"/>
+      <c r="AQ3" s="31"/>
+      <c r="AR3" s="31"/>
+      <c r="AS3" s="31"/>
+      <c r="AT3" s="31"/>
+      <c r="AU3" s="31"/>
+      <c r="AV3" s="31"/>
+      <c r="AW3" s="31"/>
+      <c r="AX3" s="31"/>
+      <c r="AY3" s="31"/>
+      <c r="AZ3" s="31"/>
+      <c r="BA3" s="31"/>
+      <c r="BB3" s="31"/>
+      <c r="BC3" s="31"/>
+      <c r="BD3" s="31"/>
+      <c r="BE3" s="31"/>
+      <c r="BF3" s="31"/>
+      <c r="BG3" s="31"/>
+      <c r="BH3" s="31"/>
     </row>
     <row r="5" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A5" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="29"/>
-      <c r="W5" s="29"/>
-      <c r="X5" s="29"/>
-      <c r="Y5" s="29"/>
-      <c r="Z5" s="29"/>
-      <c r="AA5" s="29"/>
-      <c r="AB5" s="29"/>
-      <c r="AC5" s="29"/>
-      <c r="AD5" s="29"/>
-      <c r="AE5" s="29"/>
-      <c r="AF5" s="29"/>
-      <c r="AG5" s="29"/>
-      <c r="AH5" s="29"/>
-      <c r="AI5" s="29"/>
-      <c r="AJ5" s="29"/>
-      <c r="AK5" s="29"/>
-      <c r="AL5" s="29"/>
-      <c r="AM5" s="29"/>
-      <c r="AN5" s="29"/>
-      <c r="AO5" s="29"/>
-      <c r="AP5" s="29"/>
-      <c r="AQ5" s="29"/>
-      <c r="AR5" s="29"/>
-      <c r="AS5" s="29"/>
-      <c r="AT5" s="29"/>
-      <c r="AU5" s="29"/>
-      <c r="AV5" s="29"/>
-      <c r="AW5" s="29"/>
-      <c r="AX5" s="29"/>
-      <c r="AY5" s="29"/>
-      <c r="AZ5" s="29"/>
-      <c r="BA5" s="29"/>
-      <c r="BB5" s="29"/>
-      <c r="BC5" s="29"/>
-      <c r="BD5" s="29"/>
-      <c r="BE5" s="29"/>
-      <c r="BF5" s="29"/>
-      <c r="BG5" s="29"/>
-      <c r="BH5" s="29"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="31"/>
+      <c r="P5" s="31"/>
+      <c r="Q5" s="31"/>
+      <c r="R5" s="31"/>
+      <c r="S5" s="31"/>
+      <c r="T5" s="31"/>
+      <c r="U5" s="31"/>
+      <c r="V5" s="31"/>
+      <c r="W5" s="31"/>
+      <c r="X5" s="31"/>
+      <c r="Y5" s="31"/>
+      <c r="Z5" s="31"/>
+      <c r="AA5" s="31"/>
+      <c r="AB5" s="31"/>
+      <c r="AC5" s="31"/>
+      <c r="AD5" s="31"/>
+      <c r="AE5" s="31"/>
+      <c r="AF5" s="31"/>
+      <c r="AG5" s="31"/>
+      <c r="AH5" s="31"/>
+      <c r="AI5" s="31"/>
+      <c r="AJ5" s="31"/>
+      <c r="AK5" s="31"/>
+      <c r="AL5" s="31"/>
+      <c r="AM5" s="31"/>
+      <c r="AN5" s="31"/>
+      <c r="AO5" s="31"/>
+      <c r="AP5" s="31"/>
+      <c r="AQ5" s="31"/>
+      <c r="AR5" s="31"/>
+      <c r="AS5" s="31"/>
+      <c r="AT5" s="31"/>
+      <c r="AU5" s="31"/>
+      <c r="AV5" s="31"/>
+      <c r="AW5" s="31"/>
+      <c r="AX5" s="31"/>
+      <c r="AY5" s="31"/>
+      <c r="AZ5" s="31"/>
+      <c r="BA5" s="31"/>
+      <c r="BB5" s="31"/>
+      <c r="BC5" s="31"/>
+      <c r="BD5" s="31"/>
+      <c r="BE5" s="31"/>
+      <c r="BF5" s="31"/>
+      <c r="BG5" s="31"/>
+      <c r="BH5" s="31"/>
     </row>
     <row r="6" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A6" s="28" t="str">
+      <c r="A6" s="34" t="str">
         <f>"Number of Students:  "&amp;COUNTA(B15:B47)</f>
         <v>Number of Students:  33</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="H6" s="28" t="str">
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="H6" s="34" t="str">
         <f>"Students Passing:  "&amp;COUNTIF(BH15:BH47,"PASS")</f>
         <v>Students Passing:  24</v>
       </c>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
     </row>
     <row r="7" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A7" s="28" t="str">
+      <c r="A7" s="34" t="str">
         <f>"Scheduled Class Meetings:  "&amp;15</f>
         <v>Scheduled Class Meetings:  15</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="H7" s="28" t="str">
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="H7" s="34" t="str">
         <f>"Students Not Passing:  "&amp;COUNTIF(BH15:BH47,"NOT PASS")</f>
         <v>Students Not Passing:  9</v>
       </c>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="31"/>
+      <c r="P7" s="31"/>
     </row>
     <row r="8" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A8" s="28" t="str">
+      <c r="A8" s="34" t="str">
         <f>"Average Attendance:  "&amp;TEXT(IFERROR(AVERAGE(AA15:AA47),0),"0.0%")</f>
         <v>Average Attendance:  46.3%</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="H8" s="28" t="str">
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="H8" s="34" t="str">
         <f>"Students At/Over 4-Absence Limit:  "&amp;COUNTIF(W15:W47,"&gt;=4")</f>
         <v>Students At/Over 4-Absence Limit:  4</v>
       </c>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="31"/>
+      <c r="P8" s="31"/>
     </row>
     <row r="9" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A9" s="28" t="str">
+      <c r="A9" s="34" t="str">
         <f>"Average Speaking Score:  "&amp;TEXT(IFERROR(AVERAGE(AP15:AP47),0),"0.0")</f>
         <v>Average Speaking Score:  74.5</v>
       </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="H9" s="28" t="str">
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="H9" s="34" t="str">
         <f>"Students In Progress (ungraded):  "&amp;COUNTIF(BH15:BH47,"IN PROGRESS")</f>
         <v>Students In Progress (ungraded):  0</v>
       </c>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="31"/>
+      <c r="P9" s="31"/>
     </row>
     <row r="10" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A10" s="28" t="str">
+      <c r="A10" s="34" t="str">
         <f>"Average Final Grade:  "&amp;TEXT(IFERROR(AVERAGE(BF15:BF47),0),"0.00")</f>
         <v>Average Final Grade:  55.83</v>
       </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="H10" s="28" t="str">
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="H10" s="34" t="str">
         <f>"Passing Grade Threshold:  "&amp;50</f>
         <v>Passing Grade Threshold:  50</v>
       </c>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="29"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
     </row>
     <row r="12" spans="1:60" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="35" t="s">
+      <c r="A12" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="36" t="s">
         <v>365</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="29"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
       <c r="M12" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="30" t="s">
+      <c r="N12" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="O12" s="29"/>
-      <c r="P12" s="29"/>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="29"/>
-      <c r="S12" s="29"/>
-      <c r="T12" s="29"/>
+      <c r="O12" s="31"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="31"/>
+      <c r="R12" s="31"/>
+      <c r="S12" s="31"/>
+      <c r="T12" s="31"/>
       <c r="U12" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="V12" s="31" t="s">
+      <c r="V12" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="W12" s="29"/>
-      <c r="X12" s="29"/>
-      <c r="Y12" s="29"/>
-      <c r="Z12" s="29"/>
-      <c r="AA12" s="29"/>
-      <c r="AB12" s="29"/>
-      <c r="AC12" s="29"/>
-      <c r="AD12" s="30" t="s">
+      <c r="W12" s="31"/>
+      <c r="X12" s="31"/>
+      <c r="Y12" s="31"/>
+      <c r="Z12" s="31"/>
+      <c r="AA12" s="31"/>
+      <c r="AB12" s="31"/>
+      <c r="AC12" s="31"/>
+      <c r="AD12" s="35" t="s">
         <v>515</v>
       </c>
-      <c r="AE12" s="29"/>
-      <c r="AF12" s="29"/>
-      <c r="AG12" s="29"/>
-      <c r="AH12" s="29"/>
-      <c r="AI12" s="29"/>
-      <c r="AJ12" s="29"/>
-      <c r="AK12" s="30" t="s">
+      <c r="AE12" s="31"/>
+      <c r="AF12" s="31"/>
+      <c r="AG12" s="31"/>
+      <c r="AH12" s="31"/>
+      <c r="AI12" s="31"/>
+      <c r="AJ12" s="31"/>
+      <c r="AK12" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="AL12" s="29"/>
-      <c r="AM12" s="29"/>
-      <c r="AN12" s="29"/>
-      <c r="AO12" s="29"/>
-      <c r="AP12" s="29"/>
-      <c r="AQ12" s="29"/>
-      <c r="AR12" s="30" t="s">
+      <c r="AL12" s="31"/>
+      <c r="AM12" s="31"/>
+      <c r="AN12" s="31"/>
+      <c r="AO12" s="31"/>
+      <c r="AP12" s="31"/>
+      <c r="AQ12" s="31"/>
+      <c r="AR12" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="AS12" s="29"/>
-      <c r="AT12" s="29"/>
-      <c r="AU12" s="29"/>
-      <c r="AV12" s="29"/>
-      <c r="AW12" s="29"/>
-      <c r="AX12" s="29"/>
-      <c r="AY12" s="30" t="s">
+      <c r="AS12" s="31"/>
+      <c r="AT12" s="31"/>
+      <c r="AU12" s="31"/>
+      <c r="AV12" s="31"/>
+      <c r="AW12" s="31"/>
+      <c r="AX12" s="31"/>
+      <c r="AY12" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="AZ12" s="29"/>
-      <c r="BA12" s="30" t="s">
+      <c r="AZ12" s="31"/>
+      <c r="BA12" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="BB12" s="30"/>
-      <c r="BC12" s="30"/>
-      <c r="BD12" s="30" t="s">
+      <c r="BB12" s="35"/>
+      <c r="BC12" s="35"/>
+      <c r="BD12" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="BE12" s="29"/>
-      <c r="BF12" s="37" t="s">
+      <c r="BE12" s="31"/>
+      <c r="BF12" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="BG12" s="29"/>
-      <c r="BH12" s="29"/>
+      <c r="BG12" s="31"/>
+      <c r="BH12" s="31"/>
     </row>
     <row r="13" spans="1:60" x14ac:dyDescent="0.2">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
       <c r="E13" s="22"/>
       <c r="F13" s="23"/>
       <c r="G13" s="23"/>
@@ -23942,10 +23946,10 @@
       <c r="BH13" s="23"/>
     </row>
     <row r="14" spans="1:60" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="29"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
+      <c r="A14" s="31"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
       <c r="E14" s="1" t="s">
         <v>327</v>
       </c>
@@ -23970,7 +23974,7 @@
       <c r="L14" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="M14" s="29"/>
+      <c r="M14" s="31"/>
       <c r="N14" s="1" t="s">
         <v>335</v>
       </c>
@@ -23992,7 +23996,7 @@
       <c r="T14" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="U14" s="29"/>
+      <c r="U14" s="31"/>
       <c r="V14" s="2" t="s">
         <v>33</v>
       </c>
@@ -29852,6 +29856,20 @@
   </sheetData>
   <autoFilter ref="A14:BH47" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <mergeCells count="30">
+    <mergeCell ref="H6:P6"/>
+    <mergeCell ref="E12:L12"/>
+    <mergeCell ref="V12:AC12"/>
+    <mergeCell ref="AY12:AZ12"/>
+    <mergeCell ref="BF12:BH12"/>
+    <mergeCell ref="H7:P7"/>
+    <mergeCell ref="BA12:BC12"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="AD12:AJ12"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="M12:M47"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="U12:U47"/>
     <mergeCell ref="A1:BH1"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="BD12:BE12"/>
@@ -29868,20 +29886,6 @@
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="B12:B14"/>
     <mergeCell ref="AR12:AX12"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="AD12:AJ12"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="M12:M47"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="U12:U47"/>
-    <mergeCell ref="H6:P6"/>
-    <mergeCell ref="E12:L12"/>
-    <mergeCell ref="V12:AC12"/>
-    <mergeCell ref="AY12:AZ12"/>
-    <mergeCell ref="BF12:BH12"/>
-    <mergeCell ref="H7:P7"/>
-    <mergeCell ref="BA12:BC12"/>
   </mergeCells>
   <conditionalFormatting sqref="E15:L47 N15:T47">
     <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
